--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -604,7 +604,7 @@
     <t>Type d'allergie / hypersensibilité non allergique / intolérance / idiosyncrasie</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-evenement-indesirable-previsible-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-evenement-indesirable-previsible-cisis|20260916095454</t>
   </si>
   <si>
     <t>Observation.code.nullFlavor</t>
@@ -833,7 +833,7 @@
     <t>L'élément &lt;value&gt; sera utilisé pour indiquer qu'il n'y a pas d'allergie/hypersensibilité ou que l'on ne sait pas à partir du jdv-absent-or-unknown-allergy-cisis (1.2.250.1.213.1.1.5.661).</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-absent-or-unknown-allergy-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-absent-or-unknown-allergy-cisis|20260916095454</t>
   </si>
   <si>
     <t>Observation.value.nullFlavor</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9188" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9188" uniqueCount="658">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -833,6 +833,9 @@
     <t>L'élément &lt;value&gt; sera utilisé pour indiquer qu'il n'y a pas d'allergie/hypersensibilité ou que l'on ne sait pas à partir du jdv-absent-or-unknown-allergy-cisis (1.2.250.1.213.1.1.5.661).</t>
   </si>
   <si>
+    <t>preferred</t>
+  </si>
+  <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-absent-or-unknown-allergy-cisis|20260916095454</t>
   </si>
   <si>
@@ -1443,7 +1446,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">profile:observation}
 </t>
   </si>
   <si>
@@ -10228,11 +10231,11 @@
         <v>75</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>88</v>
+        <v>266</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
@@ -10270,10 +10273,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10371,10 +10374,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10474,10 +10477,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10577,10 +10580,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10680,10 +10683,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10783,10 +10786,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10886,10 +10889,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10987,10 +10990,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11088,10 +11091,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11191,10 +11194,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11292,17 +11295,17 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>81</v>
@@ -11324,7 +11327,7 @@
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11355,7 +11358,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>75</v>
@@ -11373,7 +11376,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -11393,17 +11396,17 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>81</v>
@@ -11421,11 +11424,11 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11476,7 +11479,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -11496,17 +11499,17 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>81</v>
@@ -11528,7 +11531,7 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11559,7 +11562,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>75</v>
@@ -11577,7 +11580,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -11597,17 +11600,17 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>81</v>
@@ -11629,7 +11632,7 @@
       </c>
       <c r="L91" s="2"/>
       <c r="M91" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11680,7 +11683,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -11700,17 +11703,17 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>81</v>
@@ -11732,7 +11735,7 @@
       </c>
       <c r="L92" s="2"/>
       <c r="M92" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11763,7 +11766,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>75</v>
@@ -11781,7 +11784,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -11801,10 +11804,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11860,7 +11863,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>75</v>
@@ -11878,7 +11881,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -11898,10 +11901,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11927,13 +11930,13 @@
         <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11983,7 +11986,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -12003,17 +12006,17 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>76</v>
@@ -12031,11 +12034,11 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12086,7 +12089,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -12106,17 +12109,17 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F96" t="s" s="2">
         <v>81</v>
@@ -12138,7 +12141,7 @@
       </c>
       <c r="L96" s="2"/>
       <c r="M96" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12189,7 +12192,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -12201,7 +12204,7 @@
         <v>75</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>75</v>
@@ -12209,10 +12212,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12312,10 +12315,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12415,10 +12418,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12474,25 +12477,25 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -12512,10 +12515,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12571,25 +12574,25 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -12609,10 +12612,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12639,7 +12642,7 @@
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12690,7 +12693,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -12710,10 +12713,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12736,7 +12739,7 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12789,7 +12792,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -12809,10 +12812,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12835,7 +12838,7 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12888,7 +12891,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12908,10 +12911,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12934,7 +12937,7 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12987,7 +12990,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -13007,10 +13010,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13033,7 +13036,7 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -13086,7 +13089,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -13106,10 +13109,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13132,7 +13135,7 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -13185,7 +13188,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -13205,10 +13208,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13231,13 +13234,13 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13288,7 +13291,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -13308,10 +13311,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13409,10 +13412,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13510,10 +13513,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13611,10 +13614,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13712,10 +13715,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13815,10 +13818,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13918,10 +13921,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14021,10 +14024,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14124,10 +14127,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14225,10 +14228,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14265,7 +14268,7 @@
         <v>75</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>75</v>
@@ -14284,7 +14287,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>75</v>
@@ -14302,7 +14305,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14322,10 +14325,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14359,7 +14362,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>75</v>
@@ -14381,7 +14384,7 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>75</v>
@@ -14399,7 +14402,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -14419,10 +14422,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14498,7 +14501,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -14518,10 +14521,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14597,7 +14600,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -14617,10 +14620,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14696,7 +14699,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -14716,10 +14719,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14742,7 +14745,7 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -14795,7 +14798,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -14815,10 +14818,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14916,10 +14919,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15017,10 +15020,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15118,10 +15121,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15219,10 +15222,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15322,10 +15325,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15425,10 +15428,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15528,10 +15531,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15631,10 +15634,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15732,10 +15735,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15765,14 +15768,14 @@
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>75</v>
@@ -15791,7 +15794,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>75</v>
@@ -15809,7 +15812,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15829,10 +15832,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15908,7 +15911,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -15928,10 +15931,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15954,7 +15957,7 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -16007,7 +16010,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -16027,10 +16030,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16086,7 +16089,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>75</v>
@@ -16104,7 +16107,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -16124,10 +16127,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16203,7 +16206,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -16223,10 +16226,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16249,7 +16252,7 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -16302,7 +16305,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -16322,10 +16325,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16348,7 +16351,7 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -16401,7 +16404,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -16421,10 +16424,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16447,7 +16450,7 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16500,7 +16503,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16520,10 +16523,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16546,7 +16549,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16599,7 +16602,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -16619,10 +16622,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16720,10 +16723,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16821,10 +16824,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16922,10 +16925,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17023,10 +17026,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17126,10 +17129,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17229,10 +17232,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17332,10 +17335,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17435,10 +17438,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17536,10 +17539,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17569,14 +17572,14 @@
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q150" s="2"/>
       <c r="R150" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>75</v>
@@ -17595,7 +17598,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>75</v>
@@ -17613,7 +17616,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -17633,10 +17636,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17670,7 +17673,7 @@
       </c>
       <c r="Q151" s="2"/>
       <c r="R151" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="S151" t="s" s="2">
         <v>75</v>
@@ -17692,7 +17695,7 @@
       </c>
       <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>75</v>
@@ -17710,7 +17713,7 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -17730,10 +17733,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17759,10 +17762,10 @@
         <v>257</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17793,7 +17796,7 @@
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>75</v>
@@ -17811,7 +17814,7 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -17831,10 +17834,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17932,10 +17935,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18035,10 +18038,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18138,10 +18141,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18241,10 +18244,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18344,10 +18347,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18447,10 +18450,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18548,10 +18551,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18649,10 +18652,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18752,10 +18755,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18853,17 +18856,17 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F163" t="s" s="2">
         <v>81</v>
@@ -18885,7 +18888,7 @@
       </c>
       <c r="L163" s="2"/>
       <c r="M163" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -18916,7 +18919,7 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>75</v>
@@ -18934,7 +18937,7 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -18954,17 +18957,17 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F164" t="s" s="2">
         <v>81</v>
@@ -18982,11 +18985,11 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -19037,7 +19040,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -19057,17 +19060,17 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F165" t="s" s="2">
         <v>81</v>
@@ -19089,7 +19092,7 @@
       </c>
       <c r="L165" s="2"/>
       <c r="M165" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -19120,7 +19123,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>75</v>
@@ -19138,7 +19141,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -19158,17 +19161,17 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F166" t="s" s="2">
         <v>81</v>
@@ -19190,7 +19193,7 @@
       </c>
       <c r="L166" s="2"/>
       <c r="M166" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -19241,7 +19244,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -19261,17 +19264,17 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F167" t="s" s="2">
         <v>81</v>
@@ -19293,7 +19296,7 @@
       </c>
       <c r="L167" s="2"/>
       <c r="M167" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -19324,7 +19327,7 @@
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>75</v>
@@ -19342,7 +19345,7 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -19362,10 +19365,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19421,7 +19424,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>75</v>
@@ -19439,7 +19442,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19459,10 +19462,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19488,13 +19491,13 @@
         <v>103</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -19544,7 +19547,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -19564,17 +19567,17 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F170" t="s" s="2">
         <v>76</v>
@@ -19592,11 +19595,11 @@
         <v>75</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -19647,7 +19650,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19667,17 +19670,17 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F171" t="s" s="2">
         <v>81</v>
@@ -19699,7 +19702,7 @@
       </c>
       <c r="L171" s="2"/>
       <c r="M171" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -19750,7 +19753,7 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -19762,7 +19765,7 @@
         <v>75</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>75</v>
@@ -19770,10 +19773,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19873,10 +19876,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19976,10 +19979,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20002,7 +20005,7 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -20055,7 +20058,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -20075,10 +20078,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20101,10 +20104,10 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
@@ -20156,7 +20159,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -20176,10 +20179,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20202,11 +20205,11 @@
         <v>75</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -20257,7 +20260,7 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -20277,10 +20280,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20356,7 +20359,7 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -20376,10 +20379,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20402,7 +20405,7 @@
         <v>75</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
@@ -20455,7 +20458,7 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -20475,10 +20478,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20501,7 +20504,7 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20542,7 +20545,7 @@
         <v>75</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AC179" s="2"/>
       <c r="AD179" t="s" s="2">
@@ -20552,7 +20555,7 @@
         <v>125</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -20572,13 +20575,13 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D180" t="s" s="2">
         <v>75</v>
@@ -20600,10 +20603,10 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
@@ -20655,7 +20658,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -20675,10 +20678,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20776,10 +20779,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20877,10 +20880,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20978,10 +20981,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21079,10 +21082,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21182,10 +21185,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21285,10 +21288,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21388,10 +21391,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21491,10 +21494,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21592,10 +21595,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21632,7 +21635,7 @@
         <v>75</v>
       </c>
       <c r="S190" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="T190" t="s" s="2">
         <v>75</v>
@@ -21651,7 +21654,7 @@
       </c>
       <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>75</v>
@@ -21669,7 +21672,7 @@
         <v>75</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -21689,10 +21692,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21719,7 +21722,7 @@
       </c>
       <c r="L191" s="2"/>
       <c r="M191" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -21770,7 +21773,7 @@
         <v>75</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -21790,10 +21793,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21820,12 +21823,12 @@
       </c>
       <c r="L192" s="2"/>
       <c r="M192" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
@@ -21871,7 +21874,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -21891,10 +21894,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21970,7 +21973,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -21990,10 +21993,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22016,7 +22019,7 @@
         <v>75</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -22069,7 +22072,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -22089,10 +22092,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22115,7 +22118,7 @@
         <v>75</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -22168,7 +22171,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -22188,10 +22191,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22214,7 +22217,7 @@
         <v>75</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -22267,7 +22270,7 @@
         <v>75</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -22287,10 +22290,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22313,7 +22316,7 @@
         <v>75</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -22366,7 +22369,7 @@
         <v>75</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -22386,10 +22389,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22412,7 +22415,7 @@
         <v>75</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22465,7 +22468,7 @@
         <v>75</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -22485,10 +22488,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22511,7 +22514,7 @@
         <v>75</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22564,7 +22567,7 @@
         <v>75</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -22584,10 +22587,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22610,7 +22613,7 @@
         <v>75</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22663,7 +22666,7 @@
         <v>75</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -22683,10 +22686,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22709,7 +22712,7 @@
         <v>75</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
@@ -22762,7 +22765,7 @@
         <v>75</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -22782,10 +22785,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22808,7 +22811,7 @@
         <v>75</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -22861,7 +22864,7 @@
         <v>75</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -22881,10 +22884,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22907,7 +22910,7 @@
         <v>75</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -22960,7 +22963,7 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -22980,10 +22983,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -23006,7 +23009,7 @@
         <v>75</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -23059,7 +23062,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -23079,13 +23082,13 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D205" t="s" s="2">
         <v>75</v>
@@ -23107,10 +23110,10 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
@@ -23162,7 +23165,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -23182,10 +23185,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23283,10 +23286,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23384,10 +23387,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23485,10 +23488,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23586,10 +23589,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23689,10 +23692,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23792,10 +23795,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23895,10 +23898,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23998,10 +24001,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24099,10 +24102,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24139,7 +24142,7 @@
         <v>75</v>
       </c>
       <c r="S215" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="T215" t="s" s="2">
         <v>75</v>
@@ -24158,7 +24161,7 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>75</v>
@@ -24176,7 +24179,7 @@
         <v>75</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -24196,10 +24199,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24226,7 +24229,7 @@
       </c>
       <c r="L216" s="2"/>
       <c r="M216" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -24277,7 +24280,7 @@
         <v>75</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -24297,10 +24300,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24327,12 +24330,12 @@
       </c>
       <c r="L217" s="2"/>
       <c r="M217" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q217" s="2"/>
       <c r="R217" t="s" s="2">
@@ -24378,7 +24381,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -24398,10 +24401,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24477,7 +24480,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -24497,10 +24500,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24523,7 +24526,7 @@
         <v>75</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24576,7 +24579,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -24596,10 +24599,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24622,7 +24625,7 @@
         <v>75</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24675,7 +24678,7 @@
         <v>75</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -24695,10 +24698,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24721,7 +24724,7 @@
         <v>75</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24774,7 +24777,7 @@
         <v>75</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -24794,10 +24797,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24820,7 +24823,7 @@
         <v>75</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24873,7 +24876,7 @@
         <v>75</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -24893,10 +24896,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24919,7 +24922,7 @@
         <v>75</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24972,7 +24975,7 @@
         <v>75</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -24992,10 +24995,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -25018,7 +25021,7 @@
         <v>75</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -25071,7 +25074,7 @@
         <v>75</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -25091,10 +25094,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25117,7 +25120,7 @@
         <v>75</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -25170,7 +25173,7 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -25190,10 +25193,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25216,7 +25219,7 @@
         <v>75</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -25269,7 +25272,7 @@
         <v>75</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -25289,10 +25292,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25315,7 +25318,7 @@
         <v>75</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -25368,7 +25371,7 @@
         <v>75</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -25388,10 +25391,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25414,7 +25417,7 @@
         <v>75</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -25467,7 +25470,7 @@
         <v>75</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -25487,10 +25490,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25513,7 +25516,7 @@
         <v>75</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -25566,7 +25569,7 @@
         <v>75</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -25586,13 +25589,13 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D230" t="s" s="2">
         <v>75</v>
@@ -25614,10 +25617,10 @@
         <v>75</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M230" s="2"/>
       <c r="N230" s="2"/>
@@ -25669,7 +25672,7 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -25689,10 +25692,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25790,10 +25793,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25891,10 +25894,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25992,10 +25995,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26093,10 +26096,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -26196,10 +26199,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26299,10 +26302,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26402,10 +26405,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26505,10 +26508,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26606,10 +26609,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26646,7 +26649,7 @@
         <v>75</v>
       </c>
       <c r="S240" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="T240" t="s" s="2">
         <v>75</v>
@@ -26665,7 +26668,7 @@
       </c>
       <c r="Y240" s="2"/>
       <c r="Z240" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>75</v>
@@ -26683,7 +26686,7 @@
         <v>75</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>76</v>
@@ -26703,10 +26706,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26733,7 +26736,7 @@
       </c>
       <c r="L241" s="2"/>
       <c r="M241" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -26745,7 +26748,7 @@
         <v>75</v>
       </c>
       <c r="S241" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T241" t="s" s="2">
         <v>75</v>
@@ -26784,7 +26787,7 @@
         <v>75</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -26804,10 +26807,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26834,12 +26837,12 @@
       </c>
       <c r="L242" s="2"/>
       <c r="M242" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q242" s="2"/>
       <c r="R242" t="s" s="2">
@@ -26885,7 +26888,7 @@
         <v>75</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -26905,10 +26908,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -26984,7 +26987,7 @@
         <v>75</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -27004,10 +27007,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27030,7 +27033,7 @@
         <v>75</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
@@ -27083,7 +27086,7 @@
         <v>75</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
@@ -27103,10 +27106,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27129,7 +27132,7 @@
         <v>75</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
@@ -27182,7 +27185,7 @@
         <v>75</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
@@ -27202,10 +27205,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27228,7 +27231,7 @@
         <v>75</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
@@ -27281,7 +27284,7 @@
         <v>75</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -27301,10 +27304,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27327,7 +27330,7 @@
         <v>75</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
@@ -27380,7 +27383,7 @@
         <v>75</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
@@ -27400,10 +27403,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -27426,7 +27429,7 @@
         <v>75</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
@@ -27479,7 +27482,7 @@
         <v>75</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>81</v>
@@ -27499,10 +27502,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -27525,7 +27528,7 @@
         <v>75</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
@@ -27578,7 +27581,7 @@
         <v>75</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>81</v>
@@ -27598,10 +27601,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -27624,7 +27627,7 @@
         <v>75</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
@@ -27677,7 +27680,7 @@
         <v>75</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>81</v>
@@ -27697,10 +27700,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -27723,7 +27726,7 @@
         <v>75</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
@@ -27776,7 +27779,7 @@
         <v>75</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>81</v>
@@ -27796,10 +27799,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -27822,7 +27825,7 @@
         <v>75</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
@@ -27875,7 +27878,7 @@
         <v>75</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>81</v>
@@ -27895,10 +27898,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -27921,7 +27924,7 @@
         <v>75</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
@@ -27974,7 +27977,7 @@
         <v>75</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>81</v>
@@ -27994,10 +27997,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -28020,7 +28023,7 @@
         <v>75</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L254" s="2"/>
       <c r="M254" s="2"/>
@@ -28073,7 +28076,7 @@
         <v>75</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>81</v>
@@ -28093,13 +28096,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>75</v>
@@ -28121,10 +28124,10 @@
         <v>75</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
@@ -28176,7 +28179,7 @@
         <v>75</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>81</v>
@@ -28196,10 +28199,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -28297,10 +28300,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -28398,10 +28401,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -28499,10 +28502,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -28600,10 +28603,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -28703,10 +28706,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -28806,10 +28809,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -28909,10 +28912,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -29012,10 +29015,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -29113,10 +29116,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -29153,7 +29156,7 @@
         <v>75</v>
       </c>
       <c r="S265" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="T265" t="s" s="2">
         <v>75</v>
@@ -29172,7 +29175,7 @@
       </c>
       <c r="Y265" s="2"/>
       <c r="Z265" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>75</v>
@@ -29190,7 +29193,7 @@
         <v>75</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>76</v>
@@ -29210,10 +29213,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -29240,7 +29243,7 @@
       </c>
       <c r="L266" s="2"/>
       <c r="M266" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" s="2"/>
@@ -29252,7 +29255,7 @@
         <v>75</v>
       </c>
       <c r="S266" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T266" t="s" s="2">
         <v>75</v>
@@ -29291,7 +29294,7 @@
         <v>75</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>81</v>
@@ -29311,10 +29314,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -29341,12 +29344,12 @@
       </c>
       <c r="L267" s="2"/>
       <c r="M267" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q267" s="2"/>
       <c r="R267" t="s" s="2">
@@ -29392,7 +29395,7 @@
         <v>75</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>81</v>
@@ -29412,10 +29415,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -29491,7 +29494,7 @@
         <v>75</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>81</v>
@@ -29511,10 +29514,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -29537,7 +29540,7 @@
         <v>75</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L269" s="2"/>
       <c r="M269" s="2"/>
@@ -29590,7 +29593,7 @@
         <v>75</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>81</v>
@@ -29610,10 +29613,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -29636,7 +29639,7 @@
         <v>75</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L270" s="2"/>
       <c r="M270" s="2"/>
@@ -29689,7 +29692,7 @@
         <v>75</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>81</v>
@@ -29709,10 +29712,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -29735,7 +29738,7 @@
         <v>75</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L271" s="2"/>
       <c r="M271" s="2"/>
@@ -29788,7 +29791,7 @@
         <v>75</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>81</v>
@@ -29808,10 +29811,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -29834,7 +29837,7 @@
         <v>75</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L272" s="2"/>
       <c r="M272" s="2"/>
@@ -29887,7 +29890,7 @@
         <v>75</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>81</v>
@@ -29907,10 +29910,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -29933,7 +29936,7 @@
         <v>75</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L273" s="2"/>
       <c r="M273" s="2"/>
@@ -29986,7 +29989,7 @@
         <v>75</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>81</v>
@@ -30006,10 +30009,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -30032,7 +30035,7 @@
         <v>75</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L274" s="2"/>
       <c r="M274" s="2"/>
@@ -30085,7 +30088,7 @@
         <v>75</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>81</v>
@@ -30105,10 +30108,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -30131,7 +30134,7 @@
         <v>75</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L275" s="2"/>
       <c r="M275" s="2"/>
@@ -30184,7 +30187,7 @@
         <v>75</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>81</v>
@@ -30204,10 +30207,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -30230,7 +30233,7 @@
         <v>75</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L276" s="2"/>
       <c r="M276" s="2"/>
@@ -30283,7 +30286,7 @@
         <v>75</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>81</v>
@@ -30303,10 +30306,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -30329,7 +30332,7 @@
         <v>75</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L277" s="2"/>
       <c r="M277" s="2"/>
@@ -30382,7 +30385,7 @@
         <v>75</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>81</v>
@@ -30402,10 +30405,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -30428,7 +30431,7 @@
         <v>75</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
@@ -30481,7 +30484,7 @@
         <v>75</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>81</v>
@@ -30501,10 +30504,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -30527,7 +30530,7 @@
         <v>75</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
@@ -30580,7 +30583,7 @@
         <v>75</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>81</v>
@@ -30600,10 +30603,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -30626,7 +30629,7 @@
         <v>75</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
@@ -30679,7 +30682,7 @@
         <v>75</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>81</v>
@@ -30699,10 +30702,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -30725,7 +30728,7 @@
         <v>75</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L281" s="2"/>
       <c r="M281" s="2"/>
@@ -30778,7 +30781,7 @@
         <v>75</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>81</v>
@@ -30798,10 +30801,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -30824,7 +30827,7 @@
         <v>75</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L282" s="2"/>
       <c r="M282" s="2"/>
@@ -30877,7 +30880,7 @@
         <v>75</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>81</v>
@@ -30897,10 +30900,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -30923,11 +30926,11 @@
         <v>75</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L283" s="2"/>
       <c r="M283" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
@@ -30978,7 +30981,7 @@
         <v>75</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>81</v>
@@ -30998,10 +31001,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -31099,10 +31102,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -31200,10 +31203,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -31301,10 +31304,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -31402,10 +31405,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -31505,10 +31508,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -31608,10 +31611,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -31711,10 +31714,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -31814,10 +31817,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -31915,10 +31918,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -31952,7 +31955,7 @@
       </c>
       <c r="Q293" s="2"/>
       <c r="R293" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="S293" t="s" s="2">
         <v>75</v>
@@ -31974,7 +31977,7 @@
       </c>
       <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>75</v>
@@ -31992,7 +31995,7 @@
         <v>75</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>81</v>
@@ -32012,10 +32015,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -32038,7 +32041,7 @@
         <v>75</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
@@ -32091,7 +32094,7 @@
         <v>75</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>76</v>
@@ -32111,10 +32114,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -32137,7 +32140,7 @@
         <v>75</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L295" s="2"/>
       <c r="M295" s="2"/>
@@ -32190,7 +32193,7 @@
         <v>75</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>81</v>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
